--- a/results/components/gene_names/p2s9.xlsx
+++ b/results/components/gene_names/p2s9.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>gene1</t>
   </si>
@@ -22,184 +22,187 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>Lis-1</t>
-  </si>
-  <si>
-    <t>shn</t>
-  </si>
-  <si>
-    <t>dah</t>
-  </si>
-  <si>
-    <t>sqd</t>
-  </si>
-  <si>
-    <t>spin</t>
-  </si>
-  <si>
-    <t>dj</t>
-  </si>
-  <si>
-    <t>Nf1</t>
-  </si>
-  <si>
-    <t>slam</t>
-  </si>
-  <si>
-    <t>rdx</t>
-  </si>
-  <si>
-    <t>LCBP1</t>
-  </si>
-  <si>
-    <t>Dhc64C</t>
-  </si>
-  <si>
-    <t>Galpha73B</t>
-  </si>
-  <si>
-    <t>flw</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>sli</t>
+  </si>
+  <si>
+    <t>sax</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>asf1</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>Tak1</t>
+  </si>
+  <si>
+    <t>Tm1</t>
+  </si>
+  <si>
+    <t>inaC</t>
+  </si>
+  <si>
+    <t>sll</t>
+  </si>
+  <si>
+    <t>Sry-delta</t>
+  </si>
+  <si>
+    <t>capu</t>
+  </si>
+  <si>
+    <t>Msp-300</t>
+  </si>
+  <si>
+    <t>Ddx1</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
   </si>
   <si>
     <t>d</t>
   </si>
   <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>Dcp-1</t>
-  </si>
-  <si>
-    <t>ix</t>
-  </si>
-  <si>
-    <t>Cks30A</t>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>SelD</t>
+  </si>
+  <si>
+    <t>CkIIalpha</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>SelG</t>
   </si>
   <si>
     <t>cnc</t>
   </si>
   <si>
-    <t>Tak1</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>Idgf4</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>foxo</t>
   </si>
   <si>
     <t>thr</t>
   </si>
   <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>CG6416</t>
-  </si>
-  <si>
-    <t>CG9509</t>
-  </si>
-  <si>
-    <t>Idgf2</t>
-  </si>
-  <si>
-    <t>drm</t>
-  </si>
-  <si>
-    <t>Oseg1</t>
-  </si>
-  <si>
-    <t>Syx1A</t>
-  </si>
-  <si>
-    <t>pyd</t>
-  </si>
-  <si>
-    <t>wal</t>
-  </si>
-  <si>
-    <t>Pak</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>dl</t>
-  </si>
-  <si>
-    <t>fal</t>
-  </si>
-  <si>
-    <t>Caf1</t>
-  </si>
-  <si>
-    <t>sktl</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>Fas3</t>
-  </si>
-  <si>
-    <t>odd</t>
-  </si>
-  <si>
-    <t>emb</t>
-  </si>
-  <si>
-    <t>loco</t>
-  </si>
-  <si>
-    <t>Prm</t>
-  </si>
-  <si>
-    <t>Mer</t>
-  </si>
-  <si>
-    <t>Mlc1</t>
-  </si>
-  <si>
-    <t>CG3987</t>
-  </si>
-  <si>
-    <t>FKBP59</t>
-  </si>
-  <si>
-    <t>cas</t>
-  </si>
-  <si>
-    <t>E2f</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>dmt</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Dat</t>
-  </si>
-  <si>
-    <t>tok</t>
+    <t>Lac</t>
+  </si>
+  <si>
+    <t>kis</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>chic</t>
+  </si>
+  <si>
+    <t>Sb</t>
+  </si>
+  <si>
+    <t>siz</t>
+  </si>
+  <si>
+    <t>disco</t>
+  </si>
+  <si>
+    <t>frc</t>
+  </si>
+  <si>
+    <t>apt</t>
+  </si>
+  <si>
+    <t>Pgant35A</t>
+  </si>
+  <si>
+    <t>ine</t>
+  </si>
+  <si>
+    <t>Yp1</t>
+  </si>
+  <si>
+    <t>rdo</t>
+  </si>
+  <si>
+    <t>trc</t>
+  </si>
+  <si>
+    <t>18w</t>
+  </si>
+  <si>
+    <t>yrt</t>
+  </si>
+  <si>
+    <t>Hs6st</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -592,42 +595,42 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -664,130 +667,146 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
         <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
         <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
         <v>37</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
         <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" t="s">
         <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
         <v>45</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s">
         <v>60</v>
       </c>
-      <c r="B32" t="s">
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
         <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/results/components/gene_names/p2s9.xlsx
+++ b/results/components/gene_names/p2s9.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
   <si>
     <t>gene1</t>
   </si>
@@ -22,187 +22,253 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>sli</t>
-  </si>
-  <si>
-    <t>sax</t>
-  </si>
-  <si>
-    <t>up</t>
+    <t>trio</t>
+  </si>
+  <si>
+    <t>Su(z)12</t>
+  </si>
+  <si>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>dpld</t>
+  </si>
+  <si>
+    <t>dom</t>
+  </si>
+  <si>
+    <t>l(3)mbt</t>
+  </si>
+  <si>
+    <t>tld</t>
+  </si>
+  <si>
+    <t>CG10641</t>
+  </si>
+  <si>
+    <t>Rab5</t>
+  </si>
+  <si>
+    <t>mmy</t>
+  </si>
+  <si>
+    <t>tou</t>
+  </si>
+  <si>
+    <t>Mmp2</t>
+  </si>
+  <si>
+    <t>bap</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>puc</t>
+  </si>
+  <si>
+    <t>tra2</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>Rab7</t>
+  </si>
+  <si>
+    <t>cathD</t>
+  </si>
+  <si>
+    <t>tum</t>
+  </si>
+  <si>
+    <t>pbl</t>
+  </si>
+  <si>
+    <t>wee</t>
+  </si>
+  <si>
+    <t>wls</t>
+  </si>
+  <si>
+    <t>CG33205</t>
+  </si>
+  <si>
+    <t>CG16719</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>glu</t>
+  </si>
+  <si>
+    <t>CycE</t>
+  </si>
+  <si>
+    <t>esc</t>
+  </si>
+  <si>
+    <t>alien</t>
+  </si>
+  <si>
+    <t>Dl</t>
+  </si>
+  <si>
+    <t>Stat92E</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>emp</t>
+  </si>
+  <si>
+    <t>cactin</t>
+  </si>
+  <si>
+    <t>Su(H)</t>
+  </si>
+  <si>
+    <t>spn-A</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>E(z)</t>
+  </si>
+  <si>
+    <t>Caf1</t>
+  </si>
+  <si>
+    <t>snf</t>
+  </si>
+  <si>
+    <t>Sema-2a</t>
+  </si>
+  <si>
+    <t>Abl</t>
+  </si>
+  <si>
+    <t>BicD</t>
+  </si>
+  <si>
+    <t>rux</t>
+  </si>
+  <si>
+    <t>bigmax</t>
+  </si>
+  <si>
+    <t>spin</t>
+  </si>
+  <si>
+    <t>Pcaf</t>
+  </si>
+  <si>
+    <t>MYPT-75D</t>
+  </si>
+  <si>
+    <t>sls</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
+  </si>
+  <si>
+    <t>Apc</t>
+  </si>
+  <si>
+    <t>Dad</t>
+  </si>
+  <si>
+    <t>mus304</t>
+  </si>
+  <si>
+    <t>tok</t>
+  </si>
+  <si>
+    <t>dmt</t>
   </si>
   <si>
     <t>asf1</t>
   </si>
   <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>Tak1</t>
+    <t>lva</t>
+  </si>
+  <si>
+    <t>ttk</t>
+  </si>
+  <si>
+    <t>crol</t>
+  </si>
+  <si>
+    <t>amx</t>
+  </si>
+  <si>
+    <t>flfl</t>
+  </si>
+  <si>
+    <t>drm</t>
+  </si>
+  <si>
+    <t>CG1244</t>
+  </si>
+  <si>
+    <t>dl</t>
+  </si>
+  <si>
+    <t>numb</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>hyx</t>
+  </si>
+  <si>
+    <t>RhoL</t>
+  </si>
+  <si>
+    <t>Pvr</t>
+  </si>
+  <si>
+    <t>raw</t>
+  </si>
+  <si>
+    <t>Set2</t>
+  </si>
+  <si>
+    <t>Wnt5</t>
+  </si>
+  <si>
+    <t>chp</t>
   </si>
   <si>
     <t>Tm1</t>
   </si>
   <si>
-    <t>inaC</t>
-  </si>
-  <si>
-    <t>sll</t>
-  </si>
-  <si>
-    <t>Sry-delta</t>
-  </si>
-  <si>
-    <t>capu</t>
-  </si>
-  <si>
-    <t>Msp-300</t>
-  </si>
-  <si>
-    <t>Ddx1</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>Sema-2a</t>
-  </si>
-  <si>
-    <t>Cka</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>esc</t>
-  </si>
-  <si>
-    <t>SelD</t>
-  </si>
-  <si>
-    <t>CkIIalpha</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>eff</t>
-  </si>
-  <si>
-    <t>SelG</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>glu</t>
-  </si>
-  <si>
-    <t>numb</t>
-  </si>
-  <si>
-    <t>Idgf4</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>tld</t>
-  </si>
-  <si>
-    <t>Dad</t>
-  </si>
-  <si>
-    <t>foxo</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>Lac</t>
-  </si>
-  <si>
-    <t>kis</t>
-  </si>
-  <si>
-    <t>boss</t>
-  </si>
-  <si>
-    <t>chic</t>
-  </si>
-  <si>
-    <t>Sb</t>
-  </si>
-  <si>
-    <t>siz</t>
-  </si>
-  <si>
-    <t>disco</t>
-  </si>
-  <si>
-    <t>frc</t>
-  </si>
-  <si>
-    <t>apt</t>
-  </si>
-  <si>
-    <t>Pgant35A</t>
-  </si>
-  <si>
-    <t>ine</t>
-  </si>
-  <si>
-    <t>Yp1</t>
-  </si>
-  <si>
-    <t>rdo</t>
-  </si>
-  <si>
-    <t>trc</t>
-  </si>
-  <si>
-    <t>18w</t>
-  </si>
-  <si>
-    <t>yrt</t>
-  </si>
-  <si>
-    <t>Hs6st</t>
+    <t>hep</t>
+  </si>
+  <si>
+    <t>ftz-f1</t>
+  </si>
+  <si>
+    <t>Pka-C3</t>
+  </si>
+  <si>
+    <t>gbb</t>
+  </si>
+  <si>
+    <t>Jafrac2</t>
+  </si>
+  <si>
+    <t>ninaE</t>
   </si>
 </sst>
 </file>
@@ -534,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -566,247 +632,575 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
         <v>61</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B55" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+      <c r="B73" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
